--- a/artfynd/A 65292-2021 artfynd.xlsx
+++ b/artfynd/A 65292-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 65292-2021 artfynd.xlsx
+++ b/artfynd/A 65292-2021 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>66506075</v>
+        <v>66506089</v>
       </c>
       <c r="B2" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>405881.5566231</v>
+        <v>405882</v>
       </c>
       <c r="R2" t="n">
-        <v>7022709.702668532</v>
+        <v>7022779</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,21 +743,11 @@
           <t>2013-09-12</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2013-09-12</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -774,7 +759,7 @@
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>16187</t>
+          <t>16197</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -792,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>66506108</v>
+        <v>66506104</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,38 +788,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Väfjället, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>405858.11522537</v>
+        <v>405955</v>
       </c>
       <c r="R3" t="n">
-        <v>7023292.185757651</v>
+        <v>7023269</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -869,21 +845,11 @@
           <t>2013-09-12</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2013-09-12</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -895,7 +861,7 @@
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>16210</t>
+          <t>16207</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -913,37 +879,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>66506070</v>
+        <v>66506074</v>
       </c>
       <c r="B4" t="n">
-        <v>78533</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97449</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229748</v>
+        <v>990</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Liten hornflikmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Lophozia ascendens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Warnst.) R.M.Schust.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -953,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>405881.5566231</v>
+        <v>405882</v>
       </c>
       <c r="R4" t="n">
-        <v>7022709.702668532</v>
+        <v>7022710</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -986,21 +947,11 @@
           <t>2013-09-12</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2013-09-12</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1012,7 +963,7 @@
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>16183</t>
+          <t>16186</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1030,37 +981,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>66506078</v>
+        <v>66506079</v>
       </c>
       <c r="B5" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97449</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>990</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Liten hornflikmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lophozia ascendens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Warnst.) R.M.Schust.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1070,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>405870.6460136588</v>
+        <v>405871</v>
       </c>
       <c r="R5" t="n">
-        <v>7022767.577311509</v>
+        <v>7022768</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1103,21 +1049,11 @@
           <t>2013-09-12</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2013-09-12</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1129,7 +1065,7 @@
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>16189</t>
+          <t>16190</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1147,15 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>66506074</v>
+        <v>66506090</v>
       </c>
       <c r="B6" t="n">
-        <v>94437</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97449</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1187,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>405881.5566231</v>
+        <v>405882</v>
       </c>
       <c r="R6" t="n">
-        <v>7022709.702668532</v>
+        <v>7022779</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1220,21 +1151,11 @@
           <t>2013-09-12</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2013-09-12</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1246,7 +1167,7 @@
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>16186</t>
+          <t>16198</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1264,37 +1185,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>66506089</v>
+        <v>66506094</v>
       </c>
       <c r="B7" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97449</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>53</v>
+        <v>990</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Liten hornflikmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lophozia ascendens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Warnst.) R.M.Schust.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1304,10 +1220,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>405881.7852296742</v>
+        <v>405956</v>
       </c>
       <c r="R7" t="n">
-        <v>7022778.941451472</v>
+        <v>7022789</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1337,21 +1253,11 @@
           <t>2013-09-12</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2013-09-12</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1363,7 +1269,7 @@
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>16197</t>
+          <t>16202</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1381,37 +1287,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>66506107</v>
+        <v>66506106</v>
       </c>
       <c r="B8" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97449</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>990</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Liten hornflikmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lophozia ascendens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Warnst.) R.M.Schust.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1421,10 +1322,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>405858.11522537</v>
+        <v>405912</v>
       </c>
       <c r="R8" t="n">
-        <v>7023292.185757651</v>
+        <v>7023283</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1454,21 +1355,11 @@
           <t>2013-09-12</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2013-09-12</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1480,7 +1371,7 @@
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>16209</t>
+          <t>16208</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1501,12 +1392,7 @@
         <v>66506113</v>
       </c>
       <c r="B9" t="n">
-        <v>94437</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97449</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1538,10 +1424,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>405747.493797935</v>
+        <v>405747</v>
       </c>
       <c r="R9" t="n">
-        <v>7023281.045590743</v>
+        <v>7023281</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1571,19 +1457,9 @@
           <t>2013-09-12</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2013-09-12</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1615,37 +1491,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>66506088</v>
+        <v>66506196</v>
       </c>
       <c r="B10" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97449</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1108</v>
+        <v>990</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Liten hornflikmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lophozia ascendens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Warnst.) R.M.Schust.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1655,10 +1526,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>405881.7852296742</v>
+        <v>405896</v>
       </c>
       <c r="R10" t="n">
-        <v>7022778.941451472</v>
+        <v>7022678</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1688,21 +1559,11 @@
           <t>2013-09-12</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2013-09-12</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1714,7 +1575,7 @@
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>16196</t>
+          <t>16274</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1732,37 +1593,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>66506077</v>
+        <v>66506088</v>
       </c>
       <c r="B11" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>1108</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1772,10 +1628,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>405881.5566231</v>
+        <v>405882</v>
       </c>
       <c r="R11" t="n">
-        <v>7022709.702668532</v>
+        <v>7022779</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1805,21 +1661,11 @@
           <t>2013-09-12</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2013-09-12</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1831,7 +1677,7 @@
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>16188</t>
+          <t>16196</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1849,37 +1695,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>66506084</v>
+        <v>66506075</v>
       </c>
       <c r="B12" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1889,10 +1730,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>405866.0287983776</v>
+        <v>405882</v>
       </c>
       <c r="R12" t="n">
-        <v>7022763.665890352</v>
+        <v>7022710</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1922,21 +1763,11 @@
           <t>2013-09-12</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2013-09-12</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1948,7 +1779,7 @@
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>16194</t>
+          <t>16187</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1966,15 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>66506092</v>
+        <v>66506078</v>
       </c>
       <c r="B13" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1982,21 +1808,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2006,10 +1832,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>405956.3683471445</v>
+        <v>405871</v>
       </c>
       <c r="R13" t="n">
-        <v>7022788.896274627</v>
+        <v>7022768</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -2039,21 +1865,11 @@
           <t>2013-09-12</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2013-09-12</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2065,7 +1881,7 @@
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>16200</t>
+          <t>16189</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2083,15 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>66506091</v>
+        <v>66506083</v>
       </c>
       <c r="B14" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2099,38 +1910,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Väfjället, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>405881.7852296742</v>
+        <v>405866</v>
       </c>
       <c r="R14" t="n">
-        <v>7022778.941451472</v>
+        <v>7022764</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2160,21 +1967,11 @@
           <t>2013-09-12</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2013-09-12</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2186,7 +1983,7 @@
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>16199</t>
+          <t>16193</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2207,12 +2004,7 @@
         <v>66506109</v>
       </c>
       <c r="B15" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2248,10 +2040,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>405806.0578031743</v>
+        <v>405806</v>
       </c>
       <c r="R15" t="n">
-        <v>7023297.759004536</v>
+        <v>7023298</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2281,19 +2073,9 @@
           <t>2013-09-12</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2013-09-12</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2325,15 +2107,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>66506072</v>
+        <v>66506115</v>
       </c>
       <c r="B16" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2341,21 +2118,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2365,10 +2142,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>405881.5566231</v>
+        <v>405747</v>
       </c>
       <c r="R16" t="n">
-        <v>7022709.702668532</v>
+        <v>7023281</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2398,26 +2175,11 @@
           <t>2013-09-12</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2013-09-12</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>hackspår</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2429,7 +2191,7 @@
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>16184</t>
+          <t>16216</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2447,53 +2209,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>66506079</v>
+        <v>106607553</v>
       </c>
       <c r="B17" t="n">
-        <v>94437</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>990</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Liten hornflikmossa</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lophozia ascendens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Warnst.) R.M.Schust.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Väfjället, Jmt</t>
+          <t>Blötmon, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>405870.6460136588</v>
+        <v>405977</v>
       </c>
       <c r="R17" t="n">
-        <v>7022767.577311509</v>
+        <v>7023332</v>
       </c>
       <c r="S17" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2517,22 +2274,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2013-09-12</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-02-09</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2013-09-12</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-02-09</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2543,58 +2290,48 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>16190</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Malin Sahlin</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Via Malin Sahlin</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>66506094</v>
+        <v>66506077</v>
       </c>
       <c r="B18" t="n">
-        <v>94437</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>990</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Liten hornflikmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lophozia ascendens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Warnst.) R.M.Schust.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2604,10 +2341,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>405956.3683471445</v>
+        <v>405882</v>
       </c>
       <c r="R18" t="n">
-        <v>7022788.896274627</v>
+        <v>7022710</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2637,21 +2374,11 @@
           <t>2013-09-12</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2013-09-12</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2663,7 +2390,7 @@
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>16202</t>
+          <t>16188</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2681,54 +2408,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>66506073</v>
+        <v>66506082</v>
       </c>
       <c r="B19" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Väfjället, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>405881.5566231</v>
+        <v>405871</v>
       </c>
       <c r="R19" t="n">
-        <v>7022709.702668532</v>
+        <v>7022768</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2758,21 +2476,11 @@
           <t>2013-09-12</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2013-09-12</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2784,7 +2492,7 @@
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>16185</t>
+          <t>16192</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2802,50 +2510,49 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>66506083</v>
+        <v>66506073</v>
       </c>
       <c r="B20" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Väfjället, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>405866.0287983776</v>
+        <v>405882</v>
       </c>
       <c r="R20" t="n">
-        <v>7022763.665890352</v>
+        <v>7022710</v>
       </c>
       <c r="S20" t="n">
         <v>50</v>
@@ -2875,21 +2582,11 @@
           <t>2013-09-12</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2013-09-12</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2901,7 +2598,7 @@
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>16193</t>
+          <t>16185</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2919,15 +2616,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>66506090</v>
+        <v>66506080</v>
       </c>
       <c r="B21" t="n">
-        <v>94437</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2935,34 +2627,38 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>990</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Liten hornflikmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lophozia ascendens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Warnst.) R.M.Schust.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Väfjället, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>405881.7852296742</v>
+        <v>405871</v>
       </c>
       <c r="R21" t="n">
-        <v>7022778.941451472</v>
+        <v>7022768</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2992,21 +2688,11 @@
           <t>2013-09-12</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2013-09-12</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3018,7 +2704,7 @@
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>16198</t>
+          <t>16191</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3036,50 +2722,49 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>66506082</v>
+        <v>66506087</v>
       </c>
       <c r="B22" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Väfjället, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>405870.6460136588</v>
+        <v>405866</v>
       </c>
       <c r="R22" t="n">
-        <v>7022767.577311509</v>
+        <v>7022764</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -3109,21 +2794,11 @@
           <t>2013-09-12</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2013-09-12</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3135,7 +2810,7 @@
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>16192</t>
+          <t>16195</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3153,50 +2828,49 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>66506115</v>
+        <v>66506091</v>
       </c>
       <c r="B23" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Väfjället, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>405747.493797935</v>
+        <v>405882</v>
       </c>
       <c r="R23" t="n">
-        <v>7023281.045590743</v>
+        <v>7022779</v>
       </c>
       <c r="S23" t="n">
         <v>50</v>
@@ -3226,21 +2900,11 @@
           <t>2013-09-12</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2013-09-12</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3252,7 +2916,7 @@
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>16216</t>
+          <t>16199</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3270,19 +2934,14 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>66506080</v>
+        <v>66506093</v>
       </c>
       <c r="B24" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -3314,10 +2973,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>405870.6460136588</v>
+        <v>405956</v>
       </c>
       <c r="R24" t="n">
-        <v>7022767.577311509</v>
+        <v>7022789</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3347,21 +3006,11 @@
           <t>2013-09-12</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2013-09-12</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3373,7 +3022,7 @@
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>16191</t>
+          <t>16201</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3391,50 +3040,49 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>66506116</v>
+        <v>66506108</v>
       </c>
       <c r="B25" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Väfjället, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>405747.493797935</v>
+        <v>405858</v>
       </c>
       <c r="R25" t="n">
-        <v>7023281.045590743</v>
+        <v>7023292</v>
       </c>
       <c r="S25" t="n">
         <v>50</v>
@@ -3464,21 +3112,11 @@
           <t>2013-09-12</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2013-09-12</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3490,7 +3128,7 @@
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>16217</t>
+          <t>16210</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3508,50 +3146,49 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>66506104</v>
+        <v>66506110</v>
       </c>
       <c r="B26" t="n">
-        <v>85703</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Väfjället, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>405954.6653269421</v>
+        <v>405806</v>
       </c>
       <c r="R26" t="n">
-        <v>7023268.675414776</v>
+        <v>7023298</v>
       </c>
       <c r="S26" t="n">
         <v>50</v>
@@ -3581,21 +3218,11 @@
           <t>2013-09-12</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2013-09-12</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3607,7 +3234,7 @@
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>16207</t>
+          <t>16212</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3625,15 +3252,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>66506106</v>
+        <v>66506111</v>
       </c>
       <c r="B27" t="n">
-        <v>94437</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3641,34 +3263,38 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>990</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Liten hornflikmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lophozia ascendens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Warnst.) R.M.Schust.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Väfjället, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>405912.3164437371</v>
+        <v>405747</v>
       </c>
       <c r="R27" t="n">
-        <v>7023282.953956532</v>
+        <v>7023281</v>
       </c>
       <c r="S27" t="n">
         <v>50</v>
@@ -3698,21 +3324,11 @@
           <t>2013-09-12</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2013-09-12</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3724,7 +3340,7 @@
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>16208</t>
+          <t>16213</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3742,19 +3358,14 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>66506110</v>
+        <v>66506197</v>
       </c>
       <c r="B28" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -3786,10 +3397,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>405806.0578031743</v>
+        <v>405896</v>
       </c>
       <c r="R28" t="n">
-        <v>7023297.759004536</v>
+        <v>7022678</v>
       </c>
       <c r="S28" t="n">
         <v>50</v>
@@ -3819,21 +3430,11 @@
           <t>2013-09-12</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2013-09-12</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3845,7 +3446,7 @@
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>16212</t>
+          <t>16275</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3863,19 +3464,14 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>66506111</v>
+        <v>106607554</v>
       </c>
       <c r="B29" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -3896,24 +3492,23 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Väfjället, Jmt</t>
+          <t>Blötmon, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>405747.493797935</v>
+        <v>405908</v>
       </c>
       <c r="R29" t="n">
-        <v>7023281.045590743</v>
+        <v>7023319</v>
       </c>
       <c r="S29" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3937,22 +3532,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2013-09-12</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-02-09</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2013-09-12</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-02-09</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>rikligt i området</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3961,42 +3551,33 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AR29" t="inlineStr">
-        <is>
-          <t>16213</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Malin Sahlin</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Via Malin Sahlin</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>66506197</v>
+        <v>106607555</v>
       </c>
       <c r="B30" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -4017,24 +3598,23 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Väfjället, Jmt</t>
+          <t>Blötmon, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>405895.9438374229</v>
+        <v>405699</v>
       </c>
       <c r="R30" t="n">
-        <v>7022678.254914552</v>
+        <v>7022711</v>
       </c>
       <c r="S30" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4058,22 +3638,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2013-09-12</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-02-09</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2013-09-12</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-02-09</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>rikligt i området</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4082,60 +3657,51 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AR30" t="inlineStr">
-        <is>
-          <t>16275</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Malin Sahlin</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Via Malin Sahlin</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>66506196</v>
+        <v>66506084</v>
       </c>
       <c r="B31" t="n">
-        <v>94437</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>990</v>
+        <v>6462</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Liten hornflikmossa</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lophozia ascendens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Warnst.) R.M.Schust.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4145,10 +3711,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>405895.9438374229</v>
+        <v>405866</v>
       </c>
       <c r="R31" t="n">
-        <v>7022678.254914552</v>
+        <v>7022764</v>
       </c>
       <c r="S31" t="n">
         <v>50</v>
@@ -4178,21 +3744,11 @@
           <t>2013-09-12</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2013-09-12</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4204,7 +3760,7 @@
       </c>
       <c r="AR31" t="inlineStr">
         <is>
-          <t>16274</t>
+          <t>16194</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4222,54 +3778,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>66506093</v>
+        <v>66506107</v>
       </c>
       <c r="B32" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Väfjället, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>405956.3683471445</v>
+        <v>405858</v>
       </c>
       <c r="R32" t="n">
-        <v>7022788.896274627</v>
+        <v>7023292</v>
       </c>
       <c r="S32" t="n">
         <v>50</v>
@@ -4299,21 +3846,11 @@
           <t>2013-09-12</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2013-09-12</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4325,7 +3862,7 @@
       </c>
       <c r="AR32" t="inlineStr">
         <is>
-          <t>16201</t>
+          <t>16209</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4343,54 +3880,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>66506087</v>
+        <v>66506116</v>
       </c>
       <c r="B33" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Väfjället, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>405866.0287983776</v>
+        <v>405747</v>
       </c>
       <c r="R33" t="n">
-        <v>7022763.665890352</v>
+        <v>7023281</v>
       </c>
       <c r="S33" t="n">
         <v>50</v>
@@ -4420,21 +3948,11 @@
           <t>2013-09-12</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2013-09-12</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4446,7 +3964,7 @@
       </c>
       <c r="AR33" t="inlineStr">
         <is>
-          <t>16195</t>
+          <t>16217</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4464,32 +3982,27 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>106607548</v>
+        <v>106607552</v>
       </c>
       <c r="B34" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4508,10 +4021,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>405849.2046414915</v>
+        <v>405694</v>
       </c>
       <c r="R34" t="n">
-        <v>7022819.464876738</v>
+        <v>7022711</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4541,24 +4054,14 @@
           <t>2023-02-09</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2023-02-09</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>hack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4585,15 +4088,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>106607555</v>
+        <v>66506072</v>
       </c>
       <c r="B35" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4601,40 +4099,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Blötmon, Jmt</t>
+          <t>Väfjället, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>405698.7754608158</v>
+        <v>405882</v>
       </c>
       <c r="R35" t="n">
-        <v>7022710.569253176</v>
+        <v>7022710</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4658,27 +4153,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2023-02-09</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-09-12</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2023-02-09</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-09-12</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>rikligt i området</t>
+          <t>hackspår</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4687,34 +4172,33 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AR35" t="inlineStr">
+        <is>
+          <t>16184</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Malin Sahlin</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Via Malin Sahlin</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>106607550</v>
+        <v>106607548</v>
       </c>
       <c r="B36" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4750,10 +4234,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>405728.6263300827</v>
+        <v>405849</v>
       </c>
       <c r="R36" t="n">
-        <v>7022853.128544986</v>
+        <v>7022819</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4783,19 +4267,9 @@
           <t>2023-02-09</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2023-02-09</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
@@ -4827,15 +4301,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>106607551</v>
+        <v>106607549</v>
       </c>
       <c r="B37" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4871,10 +4340,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>405724.9351480401</v>
+        <v>405825</v>
       </c>
       <c r="R37" t="n">
-        <v>7022850.089501845</v>
+        <v>7022813</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4904,19 +4373,9 @@
           <t>2023-02-09</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2023-02-09</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -4948,15 +4407,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>106607549</v>
+        <v>106607550</v>
       </c>
       <c r="B38" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4992,10 +4446,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>405825.1512338521</v>
+        <v>405729</v>
       </c>
       <c r="R38" t="n">
-        <v>7022812.976138189</v>
+        <v>7022853</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5025,19 +4479,9 @@
           <t>2023-02-09</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2023-02-09</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -5069,15 +4513,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>106607552</v>
+        <v>106607551</v>
       </c>
       <c r="B39" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5085,16 +4524,16 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -5113,10 +4552,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>405693.8532243728</v>
+        <v>405725</v>
       </c>
       <c r="R39" t="n">
-        <v>7022711.613128311</v>
+        <v>7022850</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5146,24 +4585,14 @@
           <t>2023-02-09</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2023-02-09</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>hack</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5190,15 +4619,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>106607554</v>
+        <v>66506114</v>
       </c>
       <c r="B40" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58057</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5206,40 +4630,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Blötmon, Jmt</t>
+          <t>Väfjället, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>405907.972216142</v>
+        <v>405747</v>
       </c>
       <c r="R40" t="n">
-        <v>7023319.046742455</v>
+        <v>7023281</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5263,27 +4684,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2023-02-09</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-09-12</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2023-02-09</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>rikligt i området</t>
+          <t>2013-09-12</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5292,72 +4698,71 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AR40" t="inlineStr">
+        <is>
+          <t>16215</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Malin Sahlin</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Via Malin Sahlin</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>106607553</v>
+        <v>66506070</v>
       </c>
       <c r="B41" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80398</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2081</v>
+        <v>229748</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Blötmon, Jmt</t>
+          <t>Väfjället, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>405976.7744501354</v>
+        <v>405882</v>
       </c>
       <c r="R41" t="n">
-        <v>7023331.86637528</v>
+        <v>7022710</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5381,22 +4786,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2023-02-09</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-09-12</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2023-02-09</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-09-12</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5407,16 +4802,21 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AR41" t="inlineStr">
+        <is>
+          <t>16183</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Malin Sahlin</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Via Malin Sahlin</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>

--- a/artfynd/A 65292-2021 artfynd.xlsx
+++ b/artfynd/A 65292-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY41"/>
+  <dimension ref="A1:AZ41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66506089</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66506104</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66506074</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66506079</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66506090</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1284,6 +1314,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66506094</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1386,6 +1421,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66506106</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1488,6 +1528,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66506113</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1590,6 +1635,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66506196</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1692,6 +1742,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66506088</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1794,6 +1849,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66506075</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1896,6 +1956,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66506078</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1998,6 +2063,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66506083</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2104,6 +2174,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66506109</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2206,6 +2281,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66506115</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2303,6 +2383,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106607553</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2405,6 +2490,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66506077</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2507,6 +2597,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66506082</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2613,6 +2708,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66506073</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2719,6 +2819,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66506080</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2825,6 +2930,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66506087</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2931,6 +3041,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66506091</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3037,6 +3152,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66506093</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3143,6 +3263,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66506108</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3249,6 +3374,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66506110</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3355,6 +3485,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66506111</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3461,6 +3596,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66506197</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3567,6 +3707,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106607554</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3673,6 +3818,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106607555</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3775,6 +3925,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66506084</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3877,6 +4032,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66506107</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3979,6 +4139,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66506116</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4085,6 +4250,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106607552</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4192,6 +4362,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66506072</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4298,6 +4473,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106607548</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4404,6 +4584,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106607549</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4510,6 +4695,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106607550</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4616,6 +4806,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106607551</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4718,6 +4913,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66506114</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4820,8 +5020,55 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66506070</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>